--- a/database/final_Parameter_DB.xlsx
+++ b/database/final_Parameter_DB.xlsx
@@ -1,29 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\260108AWESIM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F06B7B35-DBF3-4A1C-AE2E-DFC369B6AC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C19166F-2D08-4CE1-9698-9A7A2EAE1B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BEE4AA1A-EC1A-4B22-8C55-E820B35A4F41}"/>
   </bookViews>
   <sheets>
     <sheet name="Wall_Assembly" sheetId="10" r:id="rId1"/>
     <sheet name="Wall_Layers_Thickness" sheetId="12" r:id="rId2"/>
-    <sheet name="Roof_Assembly" sheetId="11" r:id="rId3"/>
-    <sheet name="Roof_Layers_Thickness" sheetId="13" r:id="rId4"/>
-    <sheet name="GlazingSC" sheetId="3" r:id="rId5"/>
-    <sheet name="GlazingR" sheetId="8" r:id="rId6"/>
-    <sheet name="WWR" sheetId="4" r:id="rId7"/>
-    <sheet name="Orientation" sheetId="5" r:id="rId8"/>
-    <sheet name="Lighting" sheetId="6" r:id="rId9"/>
-    <sheet name="Equipment" sheetId="7" r:id="rId10"/>
+    <sheet name="WallR" sheetId="15" r:id="rId3"/>
+    <sheet name="Roof_Assembly" sheetId="11" r:id="rId4"/>
+    <sheet name="Roof_Layers_Thickness" sheetId="13" r:id="rId5"/>
+    <sheet name="RoofR" sheetId="16" r:id="rId6"/>
+    <sheet name="GlazingSC" sheetId="3" r:id="rId7"/>
+    <sheet name="GlazingR" sheetId="8" r:id="rId8"/>
+    <sheet name="WWR" sheetId="4" r:id="rId9"/>
+    <sheet name="Orientation" sheetId="5" r:id="rId10"/>
+    <sheet name="Lighting" sheetId="6" r:id="rId11"/>
+    <sheet name="Equipment" sheetId="7" r:id="rId12"/>
+    <sheet name="Typology" sheetId="14" r:id="rId13"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Roof_Assembly!$A$1:$H$65</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="97">
   <si>
     <t>U-Value</t>
   </si>
@@ -195,9 +201,6 @@
     <t>RCC</t>
   </si>
   <si>
-    <t>BrkTile</t>
-  </si>
-  <si>
     <t>Reinforce_Concrete_200_PUF25[ENS]</t>
   </si>
   <si>
@@ -298,21 +301,59 @@
   </si>
   <si>
     <t>Concrete</t>
+  </si>
+  <si>
+    <t>Typology</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Assembly</t>
+  </si>
+  <si>
+    <t>As Designed</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>GYP</t>
+  </si>
+  <si>
+    <t>RCC/Concrete</t>
+  </si>
+  <si>
+    <t>BrkTile/Brick</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +380,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFC9D1D9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -368,18 +415,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -411,8 +466,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4DCF7F7B-20A4-401F-8F15-E1EB8F52475A}" name="Table23" displayName="Table23" ref="B1:B9" totalsRowShown="0">
-  <autoFilter ref="B1:B9" xr:uid="{4DCF7F7B-20A4-401F-8F15-E1EB8F52475A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4DCF7F7B-20A4-401F-8F15-E1EB8F52475A}" name="Table23" displayName="Table23" ref="B1:B10" totalsRowShown="0">
+  <autoFilter ref="B1:B10" xr:uid="{4DCF7F7B-20A4-401F-8F15-E1EB8F52475A}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{8634DB1A-36BA-486B-91AB-1E0CDE02623A}" name="Light"/>
   </tableColumns>
@@ -421,8 +476,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50F27B21-1FB5-4E27-A8CF-60F2F132447E}" name="Table234" displayName="Table234" ref="B1:B12" totalsRowShown="0">
-  <autoFilter ref="B1:B12" xr:uid="{50F27B21-1FB5-4E27-A8CF-60F2F132447E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50F27B21-1FB5-4E27-A8CF-60F2F132447E}" name="Table234" displayName="Table234" ref="B1:B13" totalsRowShown="0">
+  <autoFilter ref="B1:B13" xr:uid="{50F27B21-1FB5-4E27-A8CF-60F2F132447E}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{19EF1FEB-7280-44A8-B209-6D5A85423DEC}" name="Equip"/>
   </tableColumns>
@@ -2758,12 +2813,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC7C6D8-7F46-4CE7-BB57-B5E24F170519}">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8849CFF8-3D1C-4009-9B65-37E828C0E07E}">
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -2771,7 +2825,7 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2779,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2787,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.1000000000000001</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2795,7 +2849,8 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.2</v>
+        <f>B3+45</f>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2803,7 +2858,8 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.3</v>
+        <f t="shared" ref="B5:B9" si="0">B4+45</f>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -2811,7 +2867,8 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.4</v>
+        <f t="shared" si="0"/>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -2819,7 +2876,8 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <f t="shared" si="0"/>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2827,7 +2885,8 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.6</v>
+        <f>B7+45</f>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -2835,31 +2894,108 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.7</v>
+        <f t="shared" si="0"/>
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="B2" calculatedColumn="1"/>
+  </ignoredErrors>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD325E4-92AD-42B5-8A7C-75358924326D}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2870,9 +3006,215 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC7C6D8-7F46-4CE7-BB57-B5E24F170519}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD48C1F2-F197-4467-9FD8-7D61ADE7E77F}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ref="A4:A8" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25F16FCA-609F-41F7-88A7-A95B7ECCBA6C}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.109375" bestFit="1" customWidth="1"/>
@@ -2894,65 +3236,65 @@
         <v>10</v>
       </c>
       <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>71</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>79</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>72</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>76</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>80</v>
       </c>
-      <c r="M1" t="s">
-        <v>69</v>
-      </c>
-      <c r="N1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P1" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>CONVERT(15,"mm","ft")</f>
         <v>4.9212598425196853E-2</v>
       </c>
@@ -2968,7 +3310,7 @@
         <f>840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <f>CONVERT(230,"mm","ft")</f>
         <v>0.75459317585301833</v>
       </c>
@@ -2998,14 +3340,14 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -3015,15 +3357,15 @@
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F21" si="0">0.72*5.678263243</f>
+        <f t="shared" ref="F3:F14" si="0">0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G21" si="1">1762*0.062427961</f>
+        <f t="shared" ref="G3:G14" si="1">1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H21" si="2">840* 0.000239005736</f>
+        <f t="shared" ref="H3:H14" si="2">840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
       <c r="I3" s="1">
@@ -3034,7 +3376,7 @@
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
@@ -3056,20 +3398,20 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E21" si="3">CONVERT(20,"mm","ft")</f>
+        <f t="shared" ref="E4:E14" si="3">CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="F4" s="1">
@@ -3092,7 +3434,7 @@
         <f t="shared" ref="J4:J5" si="4">0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <f t="shared" ref="K4" si="5">35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
@@ -3114,14 +3456,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -3150,7 +3492,7 @@
         <f t="shared" si="4"/>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
@@ -3172,14 +3514,14 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -3208,7 +3550,7 @@
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <f>28*0.062427961</f>
         <v>1.747982908</v>
       </c>
@@ -3230,14 +3572,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -3266,7 +3608,7 @@
         <f>0.18*5.678263243</f>
         <v>1.02208738374</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <f>642*0.062427961</f>
         <v>40.078750962000001</v>
       </c>
@@ -3288,14 +3630,14 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -3324,7 +3666,7 @@
         <f>0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <f t="shared" ref="K8:K9" si="7">28*0.062427961</f>
         <v>1.747982908</v>
       </c>
@@ -3346,14 +3688,14 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -3382,7 +3724,7 @@
         <f t="shared" ref="J9" si="8">0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <f t="shared" si="7"/>
         <v>1.747982908</v>
       </c>
@@ -3404,14 +3746,14 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -3440,7 +3782,7 @@
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
@@ -3462,14 +3804,14 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -3498,7 +3840,7 @@
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
@@ -3520,14 +3862,14 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
@@ -3556,7 +3898,7 @@
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <f>40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
@@ -3578,14 +3920,14 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B13" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
@@ -3614,7 +3956,7 @@
         <f>1.14*5.678263243</f>
         <v>6.4732200970199996</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <f>2349*0.062427961</f>
         <v>146.64328038899998</v>
       </c>
@@ -3636,14 +3978,14 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -3672,7 +4014,7 @@
         <f>0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <f>35*0.062427961</f>
         <v>2.1849786349999998</v>
       </c>
@@ -3694,52 +4036,45 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>24</v>
+      <c r="A15" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G15" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I15" s="1">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
-      <c r="J15" s="1">
-        <f>0.04*5.678263243</f>
-        <v>0.22713052972</v>
-      </c>
-      <c r="K15" s="6">
-        <f>28*0.062427961</f>
-        <v>1.747982908</v>
-      </c>
-      <c r="L15" s="2">
-        <f>1213* 0.000239005736</f>
-        <v>0.289913957768</v>
+      <c r="F15">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G15">
+        <v>118.617</v>
+      </c>
+      <c r="H15">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I15">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J15">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K15">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L15">
+        <v>0.27</v>
       </c>
       <c r="M15" s="2">
-        <v>0.49415155303615399</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="N15" s="1">
         <v>1.6E-2</v>
@@ -3752,52 +4087,44 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>25</v>
+      <c r="A16" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F16" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G16" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H16" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I16" s="1">
-        <f>CONVERT(20,"mm","ft")</f>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="J16" s="1">
-        <f>0.04*5.678263243</f>
-        <v>0.22713052972</v>
-      </c>
-      <c r="K16" s="6">
-        <f>28*0.062427961</f>
-        <v>1.747982908</v>
-      </c>
-      <c r="L16" s="2">
-        <f t="shared" ref="L16:L20" si="9">1213* 0.000239005736</f>
-        <v>0.289913957768</v>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F16">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G16">
+        <v>118.617</v>
+      </c>
+      <c r="H16">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I16">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J16">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K16">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L16">
+        <v>0.27</v>
       </c>
       <c r="M16" s="2">
-        <v>0.53352987171747301</v>
+        <v>2.860980659961547E-2</v>
       </c>
       <c r="N16" s="1">
         <v>1.6E-2</v>
@@ -3810,52 +4137,44 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>26</v>
+      <c r="A17" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F17" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G17" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H17" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I17" s="1">
-        <f>CONVERT(30,"mm","ft")</f>
-        <v>9.8425196850393706E-2</v>
-      </c>
-      <c r="J17" s="1">
-        <f>0.03*5.678263243</f>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="K17" s="6">
-        <f>35*0.062427961</f>
-        <v>2.1849786349999998</v>
-      </c>
-      <c r="L17" s="2">
-        <f t="shared" si="9"/>
-        <v>0.289913957768</v>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F17">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G17">
+        <v>118.617</v>
+      </c>
+      <c r="H17">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I17">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J17">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K17">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L17">
+        <v>0.27</v>
       </c>
       <c r="M17" s="2">
-        <v>0.57290819039879104</v>
+        <v>6.9054806599615465E-2</v>
       </c>
       <c r="N17" s="1">
         <v>1.6E-2</v>
@@ -3868,52 +4187,44 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>27</v>
+      <c r="A18" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F18" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G18" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H18" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I18" s="1">
-        <f>CONVERT(50,"mm","ft")</f>
-        <v>0.16404199475065617</v>
-      </c>
-      <c r="J18" s="1">
-        <f t="shared" ref="J18" si="10">0.03*5.678263243</f>
-        <v>0.17034789728999999</v>
-      </c>
-      <c r="K18" s="6">
-        <f>35*0.062427961</f>
-        <v>2.1849786349999998</v>
-      </c>
-      <c r="L18" s="2">
-        <f t="shared" si="9"/>
-        <v>0.289913957768</v>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F18">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G18">
+        <v>118.617</v>
+      </c>
+      <c r="H18">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I18">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J18">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K18">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L18">
+        <v>0.27</v>
       </c>
       <c r="M18" s="2">
-        <v>0.61228650908010995</v>
+        <v>0.10949980659961547</v>
       </c>
       <c r="N18" s="1">
         <v>1.6E-2</v>
@@ -3926,52 +4237,44 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>28</v>
+      <c r="A19" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F19" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G19" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H19" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I19" s="1">
-        <f>CONVERT(30,"mm","ft")</f>
-        <v>9.8425196850393706E-2</v>
-      </c>
-      <c r="J19" s="1">
-        <f>0.04*5.678263243</f>
-        <v>0.22713052972</v>
-      </c>
-      <c r="K19" s="6">
-        <f>28*0.062427961</f>
-        <v>1.747982908</v>
-      </c>
-      <c r="L19" s="2">
-        <f t="shared" si="9"/>
-        <v>0.289913957768</v>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F19">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G19">
+        <v>118.617</v>
+      </c>
+      <c r="H19">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I19">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J19">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K19">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L19">
+        <v>0.27</v>
       </c>
       <c r="M19" s="2">
-        <v>0.65166482776142898</v>
+        <v>0.14994480659961548</v>
       </c>
       <c r="N19" s="1">
         <v>1.6E-2</v>
@@ -3984,52 +4287,44 @@
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>29</v>
+      <c r="A20" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F20" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G20" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H20" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I20" s="1">
-        <f>CONVERT(50,"mm","ft")</f>
-        <v>0.16404199475065617</v>
-      </c>
-      <c r="J20" s="1">
-        <f>0.04*5.678263243</f>
-        <v>0.22713052972</v>
-      </c>
-      <c r="K20" s="6">
-        <f>28*0.062427961</f>
-        <v>1.747982908</v>
-      </c>
-      <c r="L20" s="2">
-        <f t="shared" si="9"/>
-        <v>0.289913957768</v>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F20">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G20">
+        <v>118.617</v>
+      </c>
+      <c r="H20">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I20">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J20">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K20">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L20">
+        <v>0.27</v>
       </c>
       <c r="M20" s="2">
-        <v>0.691043146442747</v>
+        <v>0.19038980659961549</v>
       </c>
       <c r="N20" s="1">
         <v>1.6E-2</v>
@@ -4042,52 +4337,44 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>30</v>
+      <c r="A21" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="3"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="F21" s="1">
-        <f t="shared" si="0"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="G21" s="1">
-        <f t="shared" si="1"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="H21" s="1">
-        <f t="shared" si="2"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="I21" s="1">
-        <f>CONVERT(200,"mm","ft")</f>
-        <v>0.65616797900262469</v>
-      </c>
-      <c r="J21" s="1">
-        <f>1.58*5.678263243</f>
-        <v>8.9716559239400002</v>
-      </c>
-      <c r="K21" s="6">
-        <f>2288*0.062427961</f>
-        <v>142.835174768</v>
-      </c>
-      <c r="L21" s="2">
-        <f>880* 0.000239005736</f>
-        <v>0.21032504767999999</v>
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F21">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G21">
+        <v>118.617</v>
+      </c>
+      <c r="H21">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J21">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K21">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L21">
+        <v>0.27</v>
       </c>
       <c r="M21" s="2">
-        <v>0.73042146512406603</v>
+        <v>0.2308348065996155</v>
       </c>
       <c r="N21" s="1">
         <v>1.6E-2</v>
@@ -4096,6 +4383,306 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="P21">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F22">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G22">
+        <v>118.617</v>
+      </c>
+      <c r="H22">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I22">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J22">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K22">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L22">
+        <v>0.27</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0.27127980659961548</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O22">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P22">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G23">
+        <v>118.617</v>
+      </c>
+      <c r="H23">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I23">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J23">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K23">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L23">
+        <v>0.27</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0.31172480659961549</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O23">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P23">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G24">
+        <v>118.617</v>
+      </c>
+      <c r="H24">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I24">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J24">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K24">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L24">
+        <v>0.27</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0.3521698065996155</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O24">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P24">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G25">
+        <v>118.617</v>
+      </c>
+      <c r="H25">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I25">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J25">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K25">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L25">
+        <v>0.27</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0.39261480659961551</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O25">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P25">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F26">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G26">
+        <v>118.617</v>
+      </c>
+      <c r="H26">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I26">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J26">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K26">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L26">
+        <v>0.27</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0.43305980659961546</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O26">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P26">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="1">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="F27">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="G27">
+        <v>118.617</v>
+      </c>
+      <c r="H27">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I27">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J27">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="K27">
+        <v>39.955199999999998</v>
+      </c>
+      <c r="L27">
+        <v>0.27</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0.47350480659961547</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O27">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P27">
         <v>0.28999999999999998</v>
       </c>
     </row>
@@ -4105,1698 +4692,122 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C8D0A7-8EE1-4751-8D99-5ECF9B5CFD63}">
-  <dimension ref="A1:H65"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C59E318-71D8-40DE-A5D8-3E45996E6EA3}">
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>B3+2.5</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ref="B5:B13" si="0">B4+2.5</f>
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
         <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E2">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F2">
-        <v>110.00166</v>
-      </c>
-      <c r="G2">
-        <v>0.20063064</v>
-      </c>
-      <c r="H2">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E3">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F3">
-        <v>118.11756</v>
-      </c>
-      <c r="G3">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H3">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E4">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F4">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G4">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H4">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E5">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F5">
-        <v>110.00166</v>
-      </c>
-      <c r="G5">
-        <v>0.20063064</v>
-      </c>
-      <c r="H5">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E6">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F6">
-        <v>110.00166</v>
-      </c>
-      <c r="G6">
-        <v>0.20063064</v>
-      </c>
-      <c r="H6">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E7">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F7">
-        <v>118.11756</v>
-      </c>
-      <c r="G7">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H7">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8">
-        <v>8.2020996999999998E-2</v>
-      </c>
-      <c r="E8">
-        <v>1.5022799999999999E-2</v>
-      </c>
-      <c r="F8">
-        <v>2.4971999999999999</v>
-      </c>
-      <c r="G8">
-        <v>0.37976514</v>
-      </c>
-      <c r="H8">
-        <v>5.4597676450000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E9">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F9">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G9">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H9">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E10">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F10">
-        <v>110.00166</v>
-      </c>
-      <c r="G10">
-        <v>0.20063064</v>
-      </c>
-      <c r="H10">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E11">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F11">
-        <v>110.00166</v>
-      </c>
-      <c r="G11">
-        <v>0.20063064</v>
-      </c>
-      <c r="H11">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E12">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F12">
-        <v>118.11756</v>
-      </c>
-      <c r="G12">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H12">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E13">
-        <v>1.5022799999999999E-2</v>
-      </c>
-      <c r="F13">
-        <v>2.4971999999999999</v>
-      </c>
-      <c r="G13">
-        <v>0.37976514</v>
-      </c>
-      <c r="H13">
-        <v>16.379302930000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E14">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F14">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G14">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H14">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E15">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F15">
-        <v>110.00166</v>
-      </c>
-      <c r="G15">
-        <v>0.20063064</v>
-      </c>
-      <c r="H15">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E16">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F16">
-        <v>110.00166</v>
-      </c>
-      <c r="G16">
-        <v>0.20063064</v>
-      </c>
-      <c r="H16">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E17">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F17">
-        <v>118.11756</v>
-      </c>
-      <c r="G17">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H17">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18">
-        <v>0.32808398999999999</v>
-      </c>
-      <c r="E18">
-        <v>1.5022799999999999E-2</v>
-      </c>
-      <c r="F18">
-        <v>2.4971999999999999</v>
-      </c>
-      <c r="G18">
-        <v>0.37976514</v>
-      </c>
-      <c r="H18">
-        <v>21.839070580000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E19">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F19">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G19">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H19">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E20">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F20">
-        <v>110.00166</v>
-      </c>
-      <c r="G20">
-        <v>0.20063064</v>
-      </c>
-      <c r="H20">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E21">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F21">
-        <v>110.00166</v>
-      </c>
-      <c r="G21">
-        <v>0.20063064</v>
-      </c>
-      <c r="H21">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E22">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F22">
-        <v>110.00166</v>
-      </c>
-      <c r="G22">
-        <v>0.20063064</v>
-      </c>
-      <c r="H22">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E23">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F23">
-        <v>118.11756</v>
-      </c>
-      <c r="G23">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H23">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E24">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F24">
-        <v>118.11756</v>
-      </c>
-      <c r="G24">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H24">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25">
-        <v>1.6404199000000001E-2</v>
-      </c>
-      <c r="E25">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F25">
-        <v>1.74804</v>
-      </c>
-      <c r="G25">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H25">
-        <v>0.74712609900000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26">
-        <v>1.6404199000000001E-2</v>
-      </c>
-      <c r="E26">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F26">
-        <v>1.74804</v>
-      </c>
-      <c r="G26">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H26">
-        <v>0.74712609900000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E27">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F27">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G27">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H27">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E28">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F28">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G28">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H28">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E29">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F29">
-        <v>110.00166</v>
-      </c>
-      <c r="G29">
-        <v>0.20063064</v>
-      </c>
-      <c r="H29">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E30">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F30">
-        <v>110.00166</v>
-      </c>
-      <c r="G30">
-        <v>0.20063064</v>
-      </c>
-      <c r="H30">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E31">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F31">
-        <v>110.00166</v>
-      </c>
-      <c r="G31">
-        <v>0.20063064</v>
-      </c>
-      <c r="H31">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E32">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F32">
-        <v>118.11756</v>
-      </c>
-      <c r="G32">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H32">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33">
-        <v>3.2808399000000002E-2</v>
-      </c>
-      <c r="E33">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F33">
-        <v>1.74804</v>
-      </c>
-      <c r="G33">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H33">
-        <v>1.4942521980000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E34">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F34">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G34">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H34">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E35">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F35">
-        <v>110.00166</v>
-      </c>
-      <c r="G35">
-        <v>0.20063064</v>
-      </c>
-      <c r="H35">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E36">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F36">
-        <v>110.00166</v>
-      </c>
-      <c r="G36">
-        <v>0.20063064</v>
-      </c>
-      <c r="H36">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E37">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F37">
-        <v>118.11756</v>
-      </c>
-      <c r="G37">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H37">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E38">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F38">
-        <v>1.74804</v>
-      </c>
-      <c r="G38">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H38">
-        <v>2.2413782960000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E39">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F39">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G39">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H39">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E40">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F40">
-        <v>110.00166</v>
-      </c>
-      <c r="G40">
-        <v>0.20063064</v>
-      </c>
-      <c r="H40">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E41">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F41">
-        <v>110.00166</v>
-      </c>
-      <c r="G41">
-        <v>0.20063064</v>
-      </c>
-      <c r="H41">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E42">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F42">
-        <v>118.11756</v>
-      </c>
-      <c r="G42">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H42">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>58</v>
-      </c>
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43">
-        <v>6.5616798000000004E-2</v>
-      </c>
-      <c r="E43">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F43">
-        <v>1.74804</v>
-      </c>
-      <c r="G43">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H43">
-        <v>2.9885043950000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E44">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F44">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G44">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H44">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>58</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E45">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F45">
-        <v>110.00166</v>
-      </c>
-      <c r="G45">
-        <v>0.20063064</v>
-      </c>
-      <c r="H45">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E46">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F46">
-        <v>110.00166</v>
-      </c>
-      <c r="G46">
-        <v>0.20063064</v>
-      </c>
-      <c r="H46">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E47">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F47">
-        <v>118.11756</v>
-      </c>
-      <c r="G47">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H47">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48">
-        <v>8.2020996999999998E-2</v>
-      </c>
-      <c r="E48">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F48">
-        <v>1.74804</v>
-      </c>
-      <c r="G48">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H48">
-        <v>3.735630494</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" t="s">
-        <v>43</v>
-      </c>
-      <c r="C49" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E49">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F49">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G49">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H49">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C50" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E50">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F50">
-        <v>110.00166</v>
-      </c>
-      <c r="G50">
-        <v>0.20063064</v>
-      </c>
-      <c r="H50">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>60</v>
-      </c>
-      <c r="B51" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E51">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F51">
-        <v>110.00166</v>
-      </c>
-      <c r="G51">
-        <v>0.20063064</v>
-      </c>
-      <c r="H51">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E52">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F52">
-        <v>118.11756</v>
-      </c>
-      <c r="G52">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H52">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" t="s">
-        <v>42</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53">
-        <v>0.164041995</v>
-      </c>
-      <c r="E53">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F53">
-        <v>1.74804</v>
-      </c>
-      <c r="G53">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H53">
-        <v>7.471260988</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" t="s">
-        <v>43</v>
-      </c>
-      <c r="C54" t="s">
-        <v>49</v>
-      </c>
-      <c r="D54">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E54">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F54">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G54">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H54">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E55">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F55">
-        <v>110.00166</v>
-      </c>
-      <c r="G55">
-        <v>0.20063064</v>
-      </c>
-      <c r="H55">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" t="s">
-        <v>38</v>
-      </c>
-      <c r="C56" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E56">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F56">
-        <v>110.00166</v>
-      </c>
-      <c r="G56">
-        <v>0.20063064</v>
-      </c>
-      <c r="H56">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E57">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F57">
-        <v>118.11756</v>
-      </c>
-      <c r="G57">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H57">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C58" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E58">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F58">
-        <v>1.74804</v>
-      </c>
-      <c r="G58">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H58">
-        <v>11.206891479999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E59">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F59">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G59">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H59">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E60">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F60">
-        <v>110.00166</v>
-      </c>
-      <c r="G60">
-        <v>0.20063064</v>
-      </c>
-      <c r="H60">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61" t="s">
-        <v>38</v>
-      </c>
-      <c r="C61" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E61">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F61">
-        <v>110.00166</v>
-      </c>
-      <c r="G61">
-        <v>0.20063064</v>
-      </c>
-      <c r="H61">
-        <v>0.118130895</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62" t="s">
-        <v>40</v>
-      </c>
-      <c r="C62" t="s">
-        <v>50</v>
-      </c>
-      <c r="D62">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E62">
-        <v>0.46108440000000001</v>
-      </c>
-      <c r="F62">
-        <v>118.11756</v>
-      </c>
-      <c r="G62">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H62">
-        <v>0.53366149900000004</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>42</v>
-      </c>
-      <c r="C63" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63">
-        <v>0.24606299200000001</v>
-      </c>
-      <c r="E63">
-        <v>2.1956400000000001E-2</v>
-      </c>
-      <c r="F63">
-        <v>1.74804</v>
-      </c>
-      <c r="G63">
-        <v>0.28972019799999998</v>
-      </c>
-      <c r="H63">
-        <v>11.206891479999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" t="s">
-        <v>43</v>
-      </c>
-      <c r="C64" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64">
-        <v>0.49212598400000002</v>
-      </c>
-      <c r="E64">
-        <v>0.91292399999999996</v>
-      </c>
-      <c r="F64">
-        <v>142.83984000000001</v>
-      </c>
-      <c r="G64">
-        <v>0.21018448000000001</v>
-      </c>
-      <c r="H64">
-        <v>0.53906566600000005</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B65" t="s">
-        <v>52</v>
-      </c>
-      <c r="C65" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65">
-        <v>4.9212598000000003E-2</v>
-      </c>
-      <c r="E65">
-        <v>0.41659380000000001</v>
-      </c>
-      <c r="F65">
-        <v>110.00166</v>
-      </c>
-      <c r="G65">
-        <v>0.20063064</v>
-      </c>
-      <c r="H65">
-        <v>0.118130895</v>
       </c>
     </row>
   </sheetData>
@@ -5805,8 +4816,1711 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C8D0A7-8EE1-4751-8D99-5ECF9B5CFD63}">
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E2">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F2">
+        <v>110.00166</v>
+      </c>
+      <c r="G2">
+        <v>0.20063064</v>
+      </c>
+      <c r="H2">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E3">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F3">
+        <v>118.11756</v>
+      </c>
+      <c r="G3">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H3">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E4">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F4">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H4">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E5">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F5">
+        <v>110.00166</v>
+      </c>
+      <c r="G5">
+        <v>0.20063064</v>
+      </c>
+      <c r="H5">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E6">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F6">
+        <v>110.00166</v>
+      </c>
+      <c r="G6">
+        <v>0.20063064</v>
+      </c>
+      <c r="H6">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E7">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F7">
+        <v>118.11756</v>
+      </c>
+      <c r="G7">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H7">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>8.2020996999999998E-2</v>
+      </c>
+      <c r="E8">
+        <v>1.5022799999999999E-2</v>
+      </c>
+      <c r="F8">
+        <v>2.4971999999999999</v>
+      </c>
+      <c r="G8">
+        <v>0.37976514</v>
+      </c>
+      <c r="H8">
+        <v>5.4597676450000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E9">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F9">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H9">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E10">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F10">
+        <v>110.00166</v>
+      </c>
+      <c r="G10">
+        <v>0.20063064</v>
+      </c>
+      <c r="H10">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E11">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F11">
+        <v>110.00166</v>
+      </c>
+      <c r="G11">
+        <v>0.20063064</v>
+      </c>
+      <c r="H11">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E12">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F12">
+        <v>118.11756</v>
+      </c>
+      <c r="G12">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H12">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E13">
+        <v>1.5022799999999999E-2</v>
+      </c>
+      <c r="F13">
+        <v>2.4971999999999999</v>
+      </c>
+      <c r="G13">
+        <v>0.37976514</v>
+      </c>
+      <c r="H13">
+        <v>16.379302930000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E14">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F14">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G14">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H14">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E15">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F15">
+        <v>110.00166</v>
+      </c>
+      <c r="G15">
+        <v>0.20063064</v>
+      </c>
+      <c r="H15">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E16">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F16">
+        <v>110.00166</v>
+      </c>
+      <c r="G16">
+        <v>0.20063064</v>
+      </c>
+      <c r="H16">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E17">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F17">
+        <v>118.11756</v>
+      </c>
+      <c r="G17">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H17">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18">
+        <v>0.32808398999999999</v>
+      </c>
+      <c r="E18">
+        <v>1.5022799999999999E-2</v>
+      </c>
+      <c r="F18">
+        <v>2.4971999999999999</v>
+      </c>
+      <c r="G18">
+        <v>0.37976514</v>
+      </c>
+      <c r="H18">
+        <v>21.839070580000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E19">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F19">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H19">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E20">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F20">
+        <v>110.00166</v>
+      </c>
+      <c r="G20">
+        <v>0.20063064</v>
+      </c>
+      <c r="H20">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E21">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F21">
+        <v>110.00166</v>
+      </c>
+      <c r="G21">
+        <v>0.20063064</v>
+      </c>
+      <c r="H21">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E22">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F22">
+        <v>110.00166</v>
+      </c>
+      <c r="G22">
+        <v>0.20063064</v>
+      </c>
+      <c r="H22">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E23">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F23">
+        <v>118.11756</v>
+      </c>
+      <c r="G23">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H23">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E24">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F24">
+        <v>118.11756</v>
+      </c>
+      <c r="G24">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H24">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25">
+        <v>1.6404199000000001E-2</v>
+      </c>
+      <c r="E25">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F25">
+        <v>1.74804</v>
+      </c>
+      <c r="G25">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H25">
+        <v>0.74712609900000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26">
+        <v>1.6404199000000001E-2</v>
+      </c>
+      <c r="E26">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F26">
+        <v>1.74804</v>
+      </c>
+      <c r="G26">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H26">
+        <v>0.74712609900000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E27">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F27">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G27">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H27">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E28">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F28">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H28">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E29">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F29">
+        <v>110.00166</v>
+      </c>
+      <c r="G29">
+        <v>0.20063064</v>
+      </c>
+      <c r="H29">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E30">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F30">
+        <v>110.00166</v>
+      </c>
+      <c r="G30">
+        <v>0.20063064</v>
+      </c>
+      <c r="H30">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E31">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F31">
+        <v>110.00166</v>
+      </c>
+      <c r="G31">
+        <v>0.20063064</v>
+      </c>
+      <c r="H31">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E32">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F32">
+        <v>118.11756</v>
+      </c>
+      <c r="G32">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H32">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33">
+        <v>3.2808399000000002E-2</v>
+      </c>
+      <c r="E33">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F33">
+        <v>1.74804</v>
+      </c>
+      <c r="G33">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H33">
+        <v>1.4942521980000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E34">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F34">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G34">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H34">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E35">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F35">
+        <v>110.00166</v>
+      </c>
+      <c r="G35">
+        <v>0.20063064</v>
+      </c>
+      <c r="H35">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E36">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F36">
+        <v>110.00166</v>
+      </c>
+      <c r="G36">
+        <v>0.20063064</v>
+      </c>
+      <c r="H36">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E37">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F37">
+        <v>118.11756</v>
+      </c>
+      <c r="G37">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H37">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E38">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F38">
+        <v>1.74804</v>
+      </c>
+      <c r="G38">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H38">
+        <v>2.2413782960000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E39">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F39">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G39">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H39">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E40">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F40">
+        <v>110.00166</v>
+      </c>
+      <c r="G40">
+        <v>0.20063064</v>
+      </c>
+      <c r="H40">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E41">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F41">
+        <v>110.00166</v>
+      </c>
+      <c r="G41">
+        <v>0.20063064</v>
+      </c>
+      <c r="H41">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E42">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F42">
+        <v>118.11756</v>
+      </c>
+      <c r="G42">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H42">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43">
+        <v>6.5616798000000004E-2</v>
+      </c>
+      <c r="E43">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F43">
+        <v>1.74804</v>
+      </c>
+      <c r="G43">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H43">
+        <v>2.9885043950000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E44">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F44">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G44">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H44">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E45">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F45">
+        <v>110.00166</v>
+      </c>
+      <c r="G45">
+        <v>0.20063064</v>
+      </c>
+      <c r="H45">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E46">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F46">
+        <v>110.00166</v>
+      </c>
+      <c r="G46">
+        <v>0.20063064</v>
+      </c>
+      <c r="H46">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E47">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F47">
+        <v>118.11756</v>
+      </c>
+      <c r="G47">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H47">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48">
+        <v>8.2020996999999998E-2</v>
+      </c>
+      <c r="E48">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F48">
+        <v>1.74804</v>
+      </c>
+      <c r="G48">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H48">
+        <v>3.735630494</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E49">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F49">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H49">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E50">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F50">
+        <v>110.00166</v>
+      </c>
+      <c r="G50">
+        <v>0.20063064</v>
+      </c>
+      <c r="H50">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E51">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F51">
+        <v>110.00166</v>
+      </c>
+      <c r="G51">
+        <v>0.20063064</v>
+      </c>
+      <c r="H51">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E52">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F52">
+        <v>118.11756</v>
+      </c>
+      <c r="G52">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H52">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53">
+        <v>0.164041995</v>
+      </c>
+      <c r="E53">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F53">
+        <v>1.74804</v>
+      </c>
+      <c r="G53">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H53">
+        <v>7.471260988</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E54">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F54">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H54">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E55">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F55">
+        <v>110.00166</v>
+      </c>
+      <c r="G55">
+        <v>0.20063064</v>
+      </c>
+      <c r="H55">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E56">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F56">
+        <v>110.00166</v>
+      </c>
+      <c r="G56">
+        <v>0.20063064</v>
+      </c>
+      <c r="H56">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E57">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F57">
+        <v>118.11756</v>
+      </c>
+      <c r="G57">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H57">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E58">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F58">
+        <v>1.74804</v>
+      </c>
+      <c r="G58">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H58">
+        <v>11.206891479999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E59">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F59">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H59">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E60">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F60">
+        <v>110.00166</v>
+      </c>
+      <c r="G60">
+        <v>0.20063064</v>
+      </c>
+      <c r="H60">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E61">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F61">
+        <v>110.00166</v>
+      </c>
+      <c r="G61">
+        <v>0.20063064</v>
+      </c>
+      <c r="H61">
+        <v>0.118130895</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E62">
+        <v>0.46108440000000001</v>
+      </c>
+      <c r="F62">
+        <v>118.11756</v>
+      </c>
+      <c r="G62">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H62">
+        <v>0.53366149900000004</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63">
+        <v>0.24606299200000001</v>
+      </c>
+      <c r="E63">
+        <v>2.1956400000000001E-2</v>
+      </c>
+      <c r="F63">
+        <v>1.74804</v>
+      </c>
+      <c r="G63">
+        <v>0.28972019799999998</v>
+      </c>
+      <c r="H63">
+        <v>11.206891479999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64">
+        <v>0.49212598400000002</v>
+      </c>
+      <c r="E64">
+        <v>0.91292399999999996</v>
+      </c>
+      <c r="F64">
+        <v>142.83984000000001</v>
+      </c>
+      <c r="G64">
+        <v>0.21018448000000001</v>
+      </c>
+      <c r="H64">
+        <v>0.53906566600000005</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65">
+        <v>4.9212598000000003E-2</v>
+      </c>
+      <c r="E65">
+        <v>0.41659380000000001</v>
+      </c>
+      <c r="F65">
+        <v>110.00166</v>
+      </c>
+      <c r="G65">
+        <v>0.20063064</v>
+      </c>
+      <c r="H65">
+        <v>0.118130895</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4D353F-88C0-490C-8C0F-0B8169DCD0F3}">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.5546875" bestFit="1" customWidth="1"/>
@@ -5830,86 +6544,86 @@
         <v>10</v>
       </c>
       <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>71</v>
       </c>
-      <c r="H1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" t="s">
         <v>76</v>
       </c>
-      <c r="K1" t="s">
-        <v>68</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" t="s">
         <v>72</v>
       </c>
-      <c r="M1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="T1" t="s">
         <v>73</v>
       </c>
-      <c r="P1" t="s">
+      <c r="U1" t="s">
         <v>77</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="V1" t="s">
         <v>81</v>
       </c>
-      <c r="R1" t="s">
-        <v>70</v>
-      </c>
-      <c r="S1" t="s">
-        <v>73</v>
-      </c>
-      <c r="T1" t="s">
-        <v>74</v>
-      </c>
-      <c r="U1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>83</v>
       </c>
-      <c r="D2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <f>CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
@@ -5929,7 +6643,7 @@
         <f>1892*0.062427961</f>
         <v>118.11370221199999</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <f>CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
@@ -5941,7 +6655,7 @@
         <f>880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <f>CONVERT(150,"mm","ft")</f>
         <v>0.49212598425196852</v>
       </c>
@@ -5958,7 +6672,7 @@
         <v>0.21032504767999999</v>
       </c>
       <c r="R2" s="1">
-        <f>N2*S2</f>
+        <f t="shared" ref="R2:R12" si="0">N2*S2</f>
         <v>4.4151850019389762</v>
       </c>
       <c r="S2" s="1">
@@ -5976,51 +6690,51 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>51</v>
+      <c r="A3" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
         <v>83</v>
       </c>
-      <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F12" si="0">CONVERT(20,"mm","ft")</f>
+        <f t="shared" ref="F3:F23" si="1">CONVERT(20,"mm","ft")</f>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" ref="G3:G12" si="1">0.72*5.678263243</f>
+        <f t="shared" ref="G3:G23" si="2">0.72*5.678263243</f>
         <v>4.0883495349599999</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H12" si="2">1762*0.062427961</f>
+        <f t="shared" ref="H3:H23" si="3">1762*0.062427961</f>
         <v>109.99806728199999</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I12" si="3">840* 0.000239005736</f>
+        <f t="shared" ref="I3:I23" si="4">840* 0.000239005736</f>
         <v>0.20076481824</v>
       </c>
       <c r="J3" s="1">
-        <f t="shared" ref="J3:J12" si="4">1892*0.062427961</f>
+        <f t="shared" ref="J3:J23" si="5">1892*0.062427961</f>
         <v>118.11370221199999</v>
       </c>
-      <c r="K3" s="5">
-        <f t="shared" ref="K3:K12" si="5">CONVERT(80,"mm","ft")</f>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K23" si="6">CONVERT(80,"mm","ft")</f>
         <v>0.26246719160104987</v>
       </c>
       <c r="L3" s="1">
-        <f t="shared" ref="L3:L12" si="6">0.8*5.678263243</f>
+        <f t="shared" ref="L3:L23" si="7">0.8*5.678263243</f>
         <v>4.5426105944000001</v>
       </c>
       <c r="M3" s="2">
-        <f t="shared" ref="M3:M12" si="7">880* 0.000239005736</f>
+        <f t="shared" ref="M3:M23" si="8">880* 0.000239005736</f>
         <v>0.21032504767999999</v>
       </c>
       <c r="N3" s="1">
@@ -6028,7 +6742,7 @@
         <v>9.8425196850393706E-2</v>
       </c>
       <c r="O3" s="1">
-        <f t="shared" ref="O3:S5" si="8">0.03*5.678263243</f>
+        <f t="shared" ref="O3:S5" si="9">0.03*5.678263243</f>
         <v>0.17034789728999999</v>
       </c>
       <c r="P3" s="1">
@@ -6040,11 +6754,11 @@
         <v>0.38001912024000001</v>
       </c>
       <c r="R3" s="1">
-        <f>N3*S3</f>
+        <f t="shared" si="0"/>
         <v>1.67665253238189E-2</v>
       </c>
       <c r="S3" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.17034789728999999</v>
       </c>
       <c r="T3" s="1">
@@ -6058,51 +6772,51 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>53</v>
+      <c r="A4" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
         <v>83</v>
       </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.20076481824</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="K4" s="5">
-        <f t="shared" si="5"/>
+      <c r="K4" s="4">
+        <f t="shared" si="6"/>
         <v>0.26246719160104987</v>
       </c>
       <c r="L4" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5426105944000001</v>
       </c>
       <c r="M4" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21032504767999999</v>
       </c>
       <c r="N4" s="1">
@@ -6110,23 +6824,23 @@
         <v>0.26246719160104987</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.17034789728999999</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" ref="P4:P5" si="9">40*0.062427961</f>
+        <f t="shared" ref="P4:P5" si="10">40*0.062427961</f>
         <v>2.4971184399999999</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" ref="Q4:Q5" si="10">1590* 0.000239005736</f>
+        <f t="shared" ref="Q4:Q5" si="11">1590* 0.000239005736</f>
         <v>0.38001912024000001</v>
       </c>
       <c r="R4" s="1">
-        <f>N4*S4</f>
+        <f t="shared" si="0"/>
         <v>4.4710734196850392E-2</v>
       </c>
       <c r="S4" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.17034789728999999</v>
       </c>
       <c r="T4" s="1">
@@ -6140,51 +6854,51 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>54</v>
+      <c r="A5" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
         <v>83</v>
       </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.20076481824</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="K5" s="5">
-        <f t="shared" si="5"/>
+      <c r="K5" s="4">
+        <f t="shared" si="6"/>
         <v>0.26246719160104987</v>
       </c>
       <c r="L5" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5426105944000001</v>
       </c>
       <c r="M5" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21032504767999999</v>
       </c>
       <c r="N5" s="1">
@@ -6192,23 +6906,23 @@
         <v>0.32808398950131235</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.17034789728999999</v>
       </c>
       <c r="P5" s="1">
+        <f t="shared" si="10"/>
+        <v>2.4971184399999999</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="11"/>
+        <v>0.38001912024000001</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="0"/>
+        <v>5.5888417746062992E-2</v>
+      </c>
+      <c r="S5" s="1">
         <f t="shared" si="9"/>
-        <v>2.4971184399999999</v>
-      </c>
-      <c r="Q5" s="1">
-        <f t="shared" si="10"/>
-        <v>0.38001912024000001</v>
-      </c>
-      <c r="R5" s="1">
-        <f>N5*S5</f>
-        <v>5.5888417746062992E-2</v>
-      </c>
-      <c r="S5" s="1">
-        <f t="shared" si="8"/>
         <v>0.17034789728999999</v>
       </c>
       <c r="T5" s="1">
@@ -6222,51 +6936,51 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>55</v>
+      <c r="A6" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.20076481824</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="K6" s="5">
-        <f t="shared" si="5"/>
+      <c r="K6" s="4">
+        <f t="shared" si="6"/>
         <v>0.26246719160104987</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5426105944000001</v>
       </c>
       <c r="M6" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21032504767999999</v>
       </c>
       <c r="N6" s="1">
@@ -6274,23 +6988,23 @@
         <v>3.2808398950131233E-2</v>
       </c>
       <c r="O6" s="1">
-        <f t="shared" ref="O6:S12" si="11">0.04*5.678263243</f>
+        <f t="shared" ref="O6:S12" si="12">0.04*5.678263243</f>
         <v>0.22713052972</v>
       </c>
       <c r="P6" s="1">
-        <f t="shared" ref="P6:P12" si="12">28*0.062427961</f>
+        <f t="shared" ref="P6:P12" si="13">28*0.062427961</f>
         <v>1.747982908</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" ref="Q6:Q12" si="13">1213* 0.000239005736</f>
+        <f t="shared" ref="Q6:Q12" si="14">1213* 0.000239005736</f>
         <v>0.289913957768</v>
       </c>
       <c r="R6" s="1">
-        <f>N6*S6</f>
+        <f t="shared" si="0"/>
         <v>7.4517890328083987E-3</v>
       </c>
       <c r="S6" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22713052972</v>
       </c>
       <c r="T6" s="1">
@@ -6304,75 +7018,75 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>56</v>
+      <c r="A7" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
         <v>83</v>
       </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N7" s="1">
+        <f t="shared" ref="N7" si="15">CONVERT(10,"mm","ft")</f>
+        <v>3.2808398950131233E-2</v>
+      </c>
+      <c r="O7" s="1">
+        <f t="shared" si="12"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="13"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="14"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R7" s="1">
         <f t="shared" si="0"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="H7" s="1">
-        <f t="shared" si="2"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="3"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="J7" s="1">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="K7" s="5">
-        <f t="shared" si="5"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="6"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="M7" s="2">
-        <f t="shared" si="7"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="N7" s="1">
-        <f t="shared" ref="N7" si="14">CONVERT(10,"mm","ft")</f>
-        <v>3.2808398950131233E-2</v>
-      </c>
-      <c r="O7" s="1">
-        <f t="shared" si="11"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="P7" s="1">
+        <v>7.4517890328083987E-3</v>
+      </c>
+      <c r="S7" s="1">
         <f t="shared" si="12"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="Q7" s="1">
-        <f t="shared" si="13"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="R7" s="1">
-        <f>N7*S7</f>
-        <v>7.4517890328083987E-3</v>
-      </c>
-      <c r="S7" s="1">
-        <f t="shared" si="11"/>
         <v>0.22713052972</v>
       </c>
       <c r="T7" s="1">
@@ -6386,75 +7100,75 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>57</v>
+      <c r="A8" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
         <v>83</v>
       </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N8" s="1">
+        <f t="shared" ref="N8:N9" si="16">CONVERT(20,"mm","ft")</f>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" si="12"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="13"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="14"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R8" s="1">
         <f t="shared" si="0"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="2"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="3"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="J8" s="1">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="5"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="6"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="M8" s="2">
-        <f t="shared" si="7"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="N8" s="1">
-        <f t="shared" ref="N8:N9" si="15">CONVERT(20,"mm","ft")</f>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="O8" s="1">
-        <f t="shared" si="11"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="P8" s="1">
+        <v>1.4903578065616797E-2</v>
+      </c>
+      <c r="S8" s="1">
         <f t="shared" si="12"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="Q8" s="1">
-        <f t="shared" si="13"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="R8" s="1">
-        <f>N8*S8</f>
-        <v>1.4903578065616797E-2</v>
-      </c>
-      <c r="S8" s="1">
-        <f t="shared" si="11"/>
         <v>0.22713052972</v>
       </c>
       <c r="T8" s="1">
@@ -6468,71 +7182,71 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>58</v>
+      <c r="A9" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="B9" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
         <v>83</v>
       </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N9" s="1">
+        <f t="shared" si="16"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="O9" s="1">
+        <f t="shared" si="12"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="13"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q9" s="1">
+        <f t="shared" si="14"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R9" s="1">
         <f t="shared" si="0"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="1"/>
-        <v>4.0883495349599999</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="2"/>
-        <v>109.99806728199999</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="3"/>
-        <v>0.20076481824</v>
-      </c>
-      <c r="J9" s="1">
-        <f t="shared" si="4"/>
-        <v>118.11370221199999</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="5"/>
-        <v>0.26246719160104987</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="6"/>
-        <v>4.5426105944000001</v>
-      </c>
-      <c r="M9" s="2">
-        <f t="shared" si="7"/>
-        <v>0.21032504767999999</v>
-      </c>
-      <c r="N9" s="1">
-        <f t="shared" si="15"/>
-        <v>6.5616797900262466E-2</v>
-      </c>
-      <c r="O9" s="1">
-        <f t="shared" si="11"/>
-        <v>0.22713052972</v>
-      </c>
-      <c r="P9" s="1">
-        <f t="shared" si="12"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="Q9" s="1">
-        <f t="shared" si="13"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="R9" s="1">
-        <f>N9*S9</f>
         <v>1.4903578065616797E-2</v>
       </c>
       <c r="S9" s="1">
@@ -6550,51 +7264,51 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>59</v>
+      <c r="A10" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
         <v>83</v>
       </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.20076481824</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="K10" s="5">
-        <f t="shared" si="5"/>
+      <c r="K10" s="4">
+        <f t="shared" si="6"/>
         <v>0.26246719160104987</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5426105944000001</v>
       </c>
       <c r="M10" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21032504767999999</v>
       </c>
       <c r="N10" s="1">
@@ -6602,23 +7316,23 @@
         <v>9.8425196850393706E-2</v>
       </c>
       <c r="O10" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22713052972</v>
       </c>
       <c r="P10" s="1">
+        <f t="shared" si="13"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q10" s="1">
+        <f t="shared" si="14"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R10" s="1">
+        <f t="shared" si="0"/>
+        <v>2.23553670984252E-2</v>
+      </c>
+      <c r="S10" s="1">
         <f t="shared" si="12"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="Q10" s="1">
-        <f t="shared" si="13"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="R10" s="1">
-        <f>N10*S10</f>
-        <v>2.23553670984252E-2</v>
-      </c>
-      <c r="S10" s="1">
-        <f t="shared" si="11"/>
         <v>0.22713052972</v>
       </c>
       <c r="T10" s="1">
@@ -6632,51 +7346,51 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>60</v>
+      <c r="A11" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
         <v>83</v>
       </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.20076481824</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="K11" s="5">
-        <f t="shared" si="5"/>
+      <c r="K11" s="4">
+        <f t="shared" si="6"/>
         <v>0.26246719160104987</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5426105944000001</v>
       </c>
       <c r="M11" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21032504767999999</v>
       </c>
       <c r="N11" s="1">
@@ -6684,23 +7398,23 @@
         <v>0.16404199475065617</v>
       </c>
       <c r="O11" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22713052972</v>
       </c>
       <c r="P11" s="1">
+        <f t="shared" si="13"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q11" s="1">
+        <f t="shared" si="14"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="0"/>
+        <v>3.7258945164041997E-2</v>
+      </c>
+      <c r="S11" s="1">
         <f t="shared" si="12"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="Q11" s="1">
-        <f t="shared" si="13"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="R11" s="1">
-        <f>N11*S11</f>
-        <v>3.7258945164041997E-2</v>
-      </c>
-      <c r="S11" s="1">
-        <f t="shared" si="11"/>
         <v>0.22713052972</v>
       </c>
       <c r="T11" s="1">
@@ -6714,51 +7428,51 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>61</v>
+      <c r="A12" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
         <v>83</v>
       </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.5616797900262466E-2</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0883495349599999</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>109.99806728199999</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.20076481824</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118.11370221199999</v>
       </c>
-      <c r="K12" s="5">
-        <f t="shared" si="5"/>
+      <c r="K12" s="4">
+        <f t="shared" si="6"/>
         <v>0.26246719160104987</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.5426105944000001</v>
       </c>
       <c r="M12" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21032504767999999</v>
       </c>
       <c r="N12" s="1">
@@ -6766,23 +7480,23 @@
         <v>0.26246719160104987</v>
       </c>
       <c r="O12" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22713052972</v>
       </c>
       <c r="P12" s="1">
+        <f t="shared" si="13"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q12" s="1">
+        <f t="shared" si="14"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R12" s="1">
+        <f t="shared" si="0"/>
+        <v>5.961431226246719E-2</v>
+      </c>
+      <c r="S12" s="1">
         <f t="shared" si="12"/>
-        <v>1.747982908</v>
-      </c>
-      <c r="Q12" s="1">
-        <f t="shared" si="13"/>
-        <v>0.289913957768</v>
-      </c>
-      <c r="R12" s="1">
-        <f>N12*S12</f>
-        <v>5.961431226246719E-2</v>
-      </c>
-      <c r="S12" s="1">
-        <f t="shared" si="11"/>
         <v>0.22713052972</v>
       </c>
       <c r="T12" s="1">
@@ -6796,127 +7510,1160 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="E13" s="7"/>
-      <c r="R13" s="1"/>
+      <c r="A13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="4">
+        <f>CONVERT(20,"mm","ft")</f>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G13" s="1">
+        <f>0.72*5.678263243</f>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H13" s="1">
+        <f>1762*0.062427961</f>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I13" s="1">
+        <f>840* 0.000239005736</f>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J13" s="1">
+        <f>1892*0.062427961</f>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K13" s="4">
+        <f>CONVERT(80,"mm","ft")</f>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L13" s="1">
+        <f>0.8*5.678263243</f>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M13" s="2">
+        <f>880* 0.000239005736</f>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N13" s="4">
+        <f>CONVERT(150,"mm","ft")</f>
+        <v>0.49212598425196852</v>
+      </c>
+      <c r="O13" s="1">
+        <f>1.58*5.678263243</f>
+        <v>8.9716559239400002</v>
+      </c>
+      <c r="P13" s="1">
+        <f>2288*0.062427961</f>
+        <v>142.835174768</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>880* 0.000239005736</f>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" ref="R13:R23" si="17">N13*S13</f>
+        <v>4.4151850019389762</v>
+      </c>
+      <c r="S13" s="1">
+        <f>1.58*5.678263243</f>
+        <v>8.9716559239400002</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U13">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V13">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N14" s="1">
+        <f>CONVERT(30,"mm","ft")</f>
+        <v>9.8425196850393706E-2</v>
+      </c>
+      <c r="O14" s="1">
+        <f t="shared" ref="O14:S16" si="18">0.03*5.678263243</f>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="P14" s="1">
+        <f>40*0.062427961</f>
+        <v>2.4971184399999999</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>1590* 0.000239005736</f>
+        <v>0.38001912024000001</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="17"/>
+        <v>1.67665253238189E-2</v>
+      </c>
+      <c r="S14" s="1">
+        <f t="shared" si="18"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="T14" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U14">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V14">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K15" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N15" s="1">
+        <f>CONVERT(80,"mm","ft")</f>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="O15" s="1">
+        <f t="shared" si="18"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="P15" s="1">
+        <f t="shared" ref="P15:P16" si="19">40*0.062427961</f>
+        <v>2.4971184399999999</v>
+      </c>
+      <c r="Q15" s="1">
+        <f t="shared" ref="Q15:Q16" si="20">1590* 0.000239005736</f>
+        <v>0.38001912024000001</v>
+      </c>
+      <c r="R15" s="1">
+        <f t="shared" si="17"/>
+        <v>4.4710734196850392E-2</v>
+      </c>
+      <c r="S15" s="1">
+        <f t="shared" si="18"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="T15" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U15">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V15">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N16" s="1">
+        <f>CONVERT(100,"mm","ft")</f>
+        <v>0.32808398950131235</v>
+      </c>
+      <c r="O16" s="1">
+        <f t="shared" si="18"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="P16" s="1">
+        <f t="shared" si="19"/>
+        <v>2.4971184399999999</v>
+      </c>
+      <c r="Q16" s="1">
+        <f t="shared" si="20"/>
+        <v>0.38001912024000001</v>
+      </c>
+      <c r="R16" s="1">
+        <f t="shared" si="17"/>
+        <v>5.5888417746062992E-2</v>
+      </c>
+      <c r="S16" s="1">
+        <f t="shared" si="18"/>
+        <v>0.17034789728999999</v>
+      </c>
+      <c r="T16" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U16">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V16">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K17" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N17" s="1">
+        <f>CONVERT(10,"mm","ft")</f>
+        <v>3.2808398950131233E-2</v>
+      </c>
+      <c r="O17" s="1">
+        <f t="shared" ref="O17:S23" si="21">0.04*5.678263243</f>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P17" s="1">
+        <f t="shared" ref="P17:P23" si="22">28*0.062427961</f>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q17" s="1">
+        <f t="shared" ref="Q17:Q23" si="23">1213* 0.000239005736</f>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R17" s="1">
+        <f t="shared" si="17"/>
+        <v>7.4517890328083987E-3</v>
+      </c>
+      <c r="S17" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T17" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U17">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V17">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K18" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N18" s="1">
+        <f t="shared" ref="N18" si="24">CONVERT(10,"mm","ft")</f>
+        <v>3.2808398950131233E-2</v>
+      </c>
+      <c r="O18" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P18" s="1">
+        <f t="shared" si="22"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q18" s="1">
+        <f t="shared" si="23"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R18" s="1">
+        <f t="shared" si="17"/>
+        <v>7.4517890328083987E-3</v>
+      </c>
+      <c r="S18" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T18" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U18">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V18">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K19" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L19" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N19" s="1">
+        <f t="shared" ref="N19:N20" si="25">CONVERT(20,"mm","ft")</f>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="O19" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P19" s="1">
+        <f t="shared" si="22"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q19" s="1">
+        <f t="shared" si="23"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R19" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4903578065616797E-2</v>
+      </c>
+      <c r="S19" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T19" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U19">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V19">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K20" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N20" s="1">
+        <f t="shared" si="25"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="O20" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P20" s="1">
+        <f t="shared" si="22"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q20" s="1">
+        <f t="shared" si="23"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R20" s="1">
+        <f t="shared" si="17"/>
+        <v>1.4903578065616797E-2</v>
+      </c>
+      <c r="S20" s="1">
+        <f>0.04*5.678263243</f>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T20" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U20">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V20">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N21" s="1">
+        <f>CONVERT(30,"mm","ft")</f>
+        <v>9.8425196850393706E-2</v>
+      </c>
+      <c r="O21" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P21" s="1">
+        <f t="shared" si="22"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q21" s="1">
+        <f t="shared" si="23"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R21" s="1">
+        <f t="shared" si="17"/>
+        <v>2.23553670984252E-2</v>
+      </c>
+      <c r="S21" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T21" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U21">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V21">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K22" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N22" s="1">
+        <f>CONVERT(50,"mm","ft")</f>
+        <v>0.16404199475065617</v>
+      </c>
+      <c r="O22" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P22" s="1">
+        <f t="shared" si="22"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q22" s="1">
+        <f t="shared" si="23"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R22" s="1">
+        <f t="shared" si="17"/>
+        <v>3.7258945164041997E-2</v>
+      </c>
+      <c r="S22" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T22" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U22">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V22">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5616797900262466E-2</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" si="2"/>
+        <v>4.0883495349599999</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="3"/>
+        <v>109.99806728199999</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20076481824</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="5"/>
+        <v>118.11370221199999</v>
+      </c>
+      <c r="K23" s="4">
+        <f t="shared" si="6"/>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="7"/>
+        <v>4.5426105944000001</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="8"/>
+        <v>0.21032504767999999</v>
+      </c>
+      <c r="N23" s="1">
+        <f>CONVERT(80,"mm","ft")</f>
+        <v>0.26246719160104987</v>
+      </c>
+      <c r="O23" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="P23" s="1">
+        <f t="shared" si="22"/>
+        <v>1.747982908</v>
+      </c>
+      <c r="Q23" s="1">
+        <f t="shared" si="23"/>
+        <v>0.289913957768</v>
+      </c>
+      <c r="R23" s="1">
+        <f t="shared" si="17"/>
+        <v>5.961431226246719E-2</v>
+      </c>
+      <c r="S23" s="1">
+        <f t="shared" si="21"/>
+        <v>0.22713052972</v>
+      </c>
+      <c r="T23" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U23">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V23">
+        <v>0.28999999999999998</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386F0D49-2EBA-4C7B-9110-F11060216CFB}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>B3+2.5</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ref="B5:B13" si="0">B4+2.5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1775773F-50F5-4561-8039-1D065600D595}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="12">
+        <f>B3*0.87</f>
+        <v>0.2175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="C4" s="12">
+        <f t="shared" ref="C4:C10" si="0">B4*0.87</f>
+        <v>0.26100000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0.25</v>
-      </c>
-      <c r="C2" s="3">
-        <f>B2/0.87</f>
-        <v>0.28735632183908044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="3">
-        <f t="shared" ref="C3:C9" si="0">B3/0.87</f>
-        <v>0.34482758620689652</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
+      <c r="B5" s="11">
         <v>0.4</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C5" s="12">
         <f t="shared" si="0"/>
-        <v>0.45977011494252878</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
+        <v>0.34800000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="11">
         <v>0.5</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C6" s="12">
         <f t="shared" si="0"/>
-        <v>0.57471264367816088</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+        <v>0.435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="11">
         <v>0.6</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C7" s="12">
         <f t="shared" si="0"/>
-        <v>0.68965517241379304</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
+        <v>0.52200000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="11">
         <v>0.7</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C8" s="12">
         <f t="shared" si="0"/>
-        <v>0.80459770114942519</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+        <v>0.60899999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="11">
         <v>0.8</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C9" s="12">
         <f t="shared" si="0"/>
-        <v>0.91954022988505757</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
+        <v>0.69600000000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B10" s="11">
         <v>0.9</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C10" s="12">
         <f t="shared" si="0"/>
-        <v>1.0344827586206897</v>
+        <v>0.78300000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -6924,9 +8671,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1C8D90-A81C-4AA2-8B37-C301DCB82A4D}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
@@ -6947,123 +8694,130 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <f>1/B2</f>
-        <v>1</v>
-      </c>
-      <c r="G2" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>0.66666999999999998</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ref="C3:C10" si="0">1/B3</f>
-        <v>1.4999925000374998</v>
+        <f>1/B3</f>
+        <v>1</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.66666999999999998</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C11" si="0">1/B4</f>
+        <v>1.4999925000374998</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>0.5</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>0.4</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>0.33333000000000002</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>3.0000300003000029</v>
       </c>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>0.28571000000000002</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>3.5000525007875116</v>
       </c>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>0.25</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>0.22222</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>4.5000450004500046</v>
       </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>0.21134</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>4.731711933377496</v>
       </c>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C11" s="2"/>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -7096,6 +8850,7 @@
     </row>
     <row r="19" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C19" s="2"/>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C20" s="2"/>
@@ -7105,15 +8860,18 @@
     </row>
     <row r="22" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4678A5D0-A5B7-4CB6-ADE5-7D5D1000F777}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
@@ -7132,238 +8890,78 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>0.4</v>
+      <c r="B2" s="3">
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
+        <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>0.5</v>
+      <c r="B3" s="3">
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
+        <f t="shared" ref="A4:A9" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>0.6</v>
+      <c r="B4" s="3">
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>0.7</v>
+      <c r="B5" s="3">
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>0.8</v>
+      <c r="B6" s="3">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="4">
-        <v>0.9</v>
-      </c>
+      <c r="B7" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8849CFF8-3D1C-4009-9B65-37E828C0E07E}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <f>B3+45</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <f t="shared" ref="B5:B9" si="0">B4+45</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <f t="shared" si="0"/>
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <f>B7+45</f>
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <f t="shared" si="0"/>
-        <v>315</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="B2" calculatedColumn="1"/>
-  </ignoredErrors>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD325E4-92AD-42B5-8A7C-75358924326D}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
